--- a/xls/square_high_un_16_tri3_15.xlsx
+++ b/xls/square_high_un_16_tri3_15.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>297</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>340</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>238</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>1266</v>
+      </c>
+      <c r="I13">
+        <v>-1.5469761517798561</v>
+      </c>
+      <c r="J13">
+        <v>-1.8922391579757647</v>
+      </c>
+      <c r="K13">
+        <v>-0.8519235282884653</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>297</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>340</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>256</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>1362</v>
+      </c>
+      <c r="I14">
+        <v>-2.182401321704366</v>
+      </c>
+      <c r="J14">
+        <v>-1.9363334902628733</v>
+      </c>
+      <c r="K14">
+        <v>-0.8631831809368057</v>
+      </c>
+    </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>11</v>

--- a/xls/square_high_un_16_tri3_15.xlsx
+++ b/xls/square_high_un_16_tri3_15.xlsx
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -456,39 +456,39 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
         <v>11</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B15" t="n">
         <v>297</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C15" t="s">
         <v>11</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D15" t="n">
         <v>340</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E15" t="s">
         <v>12</v>
       </c>
-      <c r="F16" t="n">
-        <v>340</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="F15" t="n">
+        <v>297</v>
+      </c>
+      <c r="G15" t="s">
         <v>13</v>
       </c>
-      <c r="H16" t="n">
-        <v>1842</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-1.9882264813374722</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-1.6659847343941911</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.3034109237562468</v>
+      <c r="H15" t="n">
+        <v>1596</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-2.178000347845889</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.8597953301102503</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.48137360266834667</v>
       </c>
     </row>
   </sheetData>
